--- a/docs/editor-revision/Revision_Change_Log.xlsx
+++ b/docs/editor-revision/Revision_Change_Log.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1541,6 +1541,291 @@
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>C19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>QC-3</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Manuscript</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Experimental Setup (Table 1)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Table 1 stochastic rows</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>±5% / ±40% / ±10% / ±1% 'across seeds'; generic 'assumption' sources</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Gaussian σ=5/40/10/1% with exact source symbols (price_jitter, fee_jitter, power_jitter, uptime_jitter); added Poisson block-count and Dirichlet-shares rows; each row cites scenarios.py / experiment script</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Make every parameter traceable; no invented values</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Models/Energy/scenarios.py</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>QC-6,7</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Manuscript</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Experimental Setup §E; Results §A; Discussion</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Randomness subsection; economic-PoW continuation; Discussion</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>verbose AI-style paragraphs with repetition</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>condensed prose; removed duplicated 'invariant/1-over-N' statements</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Shorten AI-style writing; reduce repetition</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>QC-7</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Manuscript</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Experimental Setup §B, §C</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Consensus/Workload; Energy/Carbon params</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>longer explanatory paragraphs</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>condensed; Table 1 retained</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Shorten Experimental Setup</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>C22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>QC-8</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Manuscript</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>refs [10], [17] DOI lines</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>'…00009 .' and '…53357-4_8 .' (stray trailing space+period)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>'…00009' and '…53357-4_8'</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Remove duplicated trailing punctuation</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>reference list</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>N/A (deletion)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>QC-8</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Manuscript</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>ref [14] IPCC URL line</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>'Website:https://www.ipcc.ch/…'</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>'Available: https://www.ipcc.ch/…'</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>IEEE-consistent URL prefix; fix run-on</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>reference list</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
